--- a/注册测试用例_最终.xlsx
+++ b/注册测试用例_最终.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>场景法</t>
+          <t>状态迁移</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">

--- a/注册测试用例_最终.xlsx
+++ b/注册测试用例_最终.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>手机号: 123</t>
+          <t>手机号: 13414764310</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
